--- a/paper/EACL Final/experiments/human_reviewer/master_blind_sheet_200.xlsx
+++ b/paper/EACL Final/experiments/human_reviewer/master_blind_sheet_200.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All 200 Queries" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 03" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 04" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 05" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 06" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 07" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 08" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_and_Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch 10" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +39,26 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -57,7 +76,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,14 +85,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B4332"/>
-        <bgColor rgb="001B4332"/>
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002D6A4F"/>
-        <bgColor rgb="002D6A4F"/>
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,8 +103,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="001B4332"/>
+        <bgColor rgb="001B4332"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D6A4F"/>
+        <bgColor rgb="002D6A4F"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,49 +146,87 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +601,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -567,7 +636,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -5815,7 +5884,10 @@
       <c r="J201" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168 F169 F170 F171 F172 F173 F174 F175 F176 F177 F178 F179 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F191 F192 F193 F194 F195 F196 F197 F198 F199 F200 F201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -5844,7 +5916,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -5879,7 +5951,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -5905,11 +5977,11 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_744</t>
+          <t>farmer_q_181</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -5919,7 +5991,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>ড্রাগন গাছে ফুল আসার পর সেগুলো লাল হয়ে কেন ঝরে পড়ছে বুঝতে পারছি না, কোনো ওষুধ বা সার দিলে কি কাজ হবে?</t>
+          <t>সরিষার ফুল আসার পর জাব পোকার আক্রমণ হয়েছে, এখন কি বিষ দেওয়া যাবে?</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -5931,21 +6003,21 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_16</t>
+          <t>farmer_q_361</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>এক বিঘা মরিচের জমি থেকে কি ৪ হাজার কেজি মরিচ পাওয়া সম্ভব..? মানে চার হাজার গাছ থেকে ৪ হাজার কেজি..? মানে ১০০ মন..?</t>
+          <t>মাটি শক্ত হইয়া গেছে, এখন কি করুম?</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -5957,21 +6029,21 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_896</t>
+          <t>farmer_q_365</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>স্যার, আমি সিরাজগঞ্জের উল্লাপাড়ার বাসিন্দা। পড়াশোনা শেষ করে বাড়িতে ফলের চাষ শুরু করতে চাচ্ছি, তাই এ বিষয়ে ভালো কোনো প্রশিক্ষণের ব্যবস্থা বা সরকারি অনুদান পাওয়ার কোনো উপায় আছে কি না জানাবেন?</t>
+          <t>ফুলকপি চাষে পোকা ধরলে কি বিষ দেওয়া ভালো না অন্য কিছু?</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -5983,11 +6055,11 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_302</t>
+          <t>farmer_q_13</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -5997,7 +6069,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>শসা গাছের গোড়ায় পচন দেখা যাচ্ছে, আমি কি কোনো জৈব পদ্ধতি ব্যবহার করতে পারি?</t>
+          <t>করলা গাছের ছোট ছোট ফল হয়ে ঝরে পরতিছে 🥲 এর প্রতিকার কিভাবে করবো??</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -6009,21 +6081,21 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_946</t>
+          <t>farmer_q_772</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>স্যার, আমার দেড় বিঘা আম্রপালি আর আধা বিঘা বারি-৪ বাগান আছে, এখন বাণিজ্যিকভাবে লাভবান হওয়ার জন্য আর কী কী জাতের আম লাগানো ভালো হবে? আমি একটু দ্বিধায় আছি, সঠিক পরামর্শ দিলে উপকৃত হতাম।</t>
+          <t>বাড়িতে একটা খুব ভালো জাতের আমড়া গাছ আছে যা বছরে দুইবার ফল দেয়, কিন্তু ঘর বড় করার জন্য গাছটা কাটতে হবে। আমি এই জাতটা বাঁচাতে চাই, আমড়া গাছে কলম করার নিয়মটা একটু বলবেন?</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -6035,21 +6107,21 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_15</t>
+          <t>farmer_q_569</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>এখন কোন জাতের শিম চাষ করা যাবে সকলের পরামর্শ চাচ্ছি আর কোন কোম্পানির?</t>
+          <t>ধানের পাতায় কেমন জানি লালচে দাগ পড়ছে, কী করমু?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -6061,21 +6133,21 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_57</t>
+          <t>farmer_q_461</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>আসসালামু আলাইকুম সার হলুদের জমিতে আগাছা নাশক মারা জাবে কি?</t>
+          <t>বেগুন গাছে পোকা লেগেছে, কোনো ভালো কীটনাশকের নাম বলবেন?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -6087,11 +6159,11 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_309</t>
+          <t>farmer_q_274</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -6101,7 +6173,7 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>তরমুজ গাছের গোড়ায় পচন ধরে গাছ হঠাৎ শুকিয়ে যাচ্ছে, কী সমাধান?</t>
+          <t>ধানের পাতায় মরিচা বা ব্লাস্ট রোগ দেখা দিয়েছে। কি করলে ফলন রক্ষা করা যাবে?</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -6113,11 +6185,11 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_775</t>
+          <t>farmer_q_687</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -6127,7 +6199,8 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>দাদা, আমার টবের মরিচ গাছে ফুল তো প্রচুর আসে, কিন্তু একটাও মরিচ দাঁড়াচ্ছে না, সব ফুল ঝরে যাচ্ছে। এর কি কোনো উপায় আছে?</t>
+          <t>ভাই, আসসালামুআলাইকুম।
+আমি একজন মাশরুম চাষী। আমার বর্তমানে ৫০০০ খরের প্যাকেট (১২*১৮) আআছে।ওয়েস্টার ws +po2 জাতের কিন্তু ফলন তুলনা মূলক অনেক কম হচ্ছে।দয়াকরে ফলন কি ভাবে বাড়ানো যায় জানাবেন কি ? মোবাইল নং ০১৭৫২-৪১২২৫৫। আপনাদের সাথে যোগাযোগের মোবাইল নং দেবেন plz.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -6139,21 +6212,21 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_834</t>
+          <t>farmer_q_603</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>আমি সিলেটে পেঁপে চাষ শুরু করতে চাচ্ছি, কোন জাতের পেঁপে দ্রুত ফলে আর বেশি ফলন দেয়? ভালো বীজ কোথা থেকে কিনবো? আর বীজতলা তৈরির পদ্ধতিসহ এক শতক জমিতে কতগুলো চারা রোপণ করা যায় তা জানাবেন।</t>
+          <t>শসা গাছে হলুদ হলুদ কি যেন হইতাছে, কোনো ওষুধ আছে?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -6165,11 +6238,11 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_414</t>
+          <t>farmer_q_572</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -6179,7 +6252,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>টমেটো গাছ হলুদ হয়ে যাচ্ছে কেন বুঝতে পারছি না, কি করবো?</t>
+          <t>কীটনাশক দেওয়ার পর বৃষ্টি আইলে কি আবার দিতে হইবো?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -6191,21 +6264,21 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_338</t>
+          <t>farmer_q_229</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>ধানের পাতায় কেমন জানি লাল দাগ হইছে, কি করুম?</t>
+          <t>আমার শসা গাছে পাতার ওপর হলুদ মোজাইক আকৃতির দাগ দেখা যাচ্ছে, এটি কি ভাইরাস?</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -6217,21 +6290,21 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_125</t>
+          <t>farmer_q_654</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>টমেটো গাছে ফল আসার পর ফল পচা শুরু হয়েছে, নিচের দিক থেকে কালো হয়ে যাচ্ছে। কী করব?</t>
+          <t>আমি জেনেছি,সুপারী গাছ ৪হাত দুরত্বে রোপণ করতে হয়।কিন্তু আমি ৩হাত দুরত্বে রোপন করে ফেলেছি।এখন কি সুপারি ধরবে?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -6243,21 +6316,21 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_325</t>
+          <t>farmer_q_950</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>বেগুন গাছের ডগা ও ফল ছিদ্রকারী পোকা দমনে জৈব বা নিরাপদ কোনো উপায় আছে কি?</t>
+          <t>ভাই, লাউ গাছ তো অনেক বড় হলো, কিন্তু একটাও ফুল ফুটছে না। কী করব?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -6269,21 +6342,21 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_216</t>
+          <t>farmer_q_404</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>শীতকালীন সবজির জন্য সার প্রয়োগের সঠিক নিয়ম কী?</t>
+          <t>সবজি বাগানে কি খৈল পচা সার দেওয়া ঠিক হবে?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -6295,11 +6368,11 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_135</t>
+          <t>farmer_q_295</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -6309,7 +6382,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>বেগুন গাছে ডগা ও ফল ছিদ্রকারী পোকা দমনে জৈব পদ্ধতি কী?</t>
+          <t>শীতকালীন সবজির জন্য এনপিকে (NPK) সারের সঠিক অনুপাত কী হওয়া উচিত?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -6321,11 +6394,11 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_63</t>
+          <t>farmer_q_739</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -6335,7 +6408,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>আমন মৌসুমে সবচেয়ে উচ্চ ফলনশীল জাত কোনটি আমন মৌসুমে ৩৫ শতাংশ জমিতে আবাদ করতে চাই</t>
+          <t>আমার লেবু গাছের পাতাগুলো হলুদ হয়ে শুকিয়ে যাচ্ছে, আর পাতার নিচে সাদা সাদা দাগ দেখা যাচ্ছে। এর জন্য কী করতে পারি?</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -6347,21 +6420,21 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_970</t>
+          <t>farmer_q_631</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>ভাই, চিটাগাং শহরে লিটোসেন আর ডিএপি সার কোথায় পাওয়া যাবে একটু বলবেন?</t>
+          <t>একটু কম খরচে কী সার দেওয়া যায়?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -6373,21 +6446,21 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_470</t>
+          <t>farmer_q_961</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>ধানের জমিতে প্রচুর আগাছা, কী ওষুধ মারলে ভালো হইবো?</t>
+          <t>আমন ধানের বীজতলায় পোকা ধরেছে, এখন কী করলে ভালো হয়?</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -6399,21 +6472,21 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_537</t>
+          <t>farmer_q_904</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>অকাল বৃষ্টিতে ধানের খুব ক্ষতি হইছে, এখন কি আর কিছু লাগানো যাবে?</t>
+          <t>ভাই, ছাদ বাগান করার ওপর কোনো ট্রেনিংয়ের ব্যবস্থা আছে কি? থাকলে কোথায় যোগাযোগ করব জানাবেন?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -6424,7 +6497,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -6453,7 +6529,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -6488,7 +6564,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -6514,21 +6590,21 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_349</t>
+          <t>farmer_q_744</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>ফল আসার আগে গাছ ঝিমিয়ে পড়ছে, কি করবো?</t>
+          <t>ড্রাগন গাছে ফুল আসার পর সেগুলো লাল হয়ে কেন ঝরে পড়ছে বুঝতে পারছি না, কোনো ওষুধ বা সার দিলে কি কাজ হবে?</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -6540,11 +6616,11 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_677</t>
+          <t>farmer_q_16</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -6554,9 +6630,7 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>আমার বাড়ীর ছাদে কিছু ফল গাছ অতি বৃষ্টি হওয়াতে
-কিছুটা দুরল হয়ে পরেছে।
-এই মুহুর্তে আমার করনিয় কি?</t>
+          <t>এক বিঘা মরিচের জমি থেকে কি ৪ হাজার কেজি মরিচ পাওয়া সম্ভব..? মানে চার হাজার গাছ থেকে ৪ হাজার কেজি..? মানে ১০০ মন..?</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -6568,11 +6642,11 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_710</t>
+          <t>farmer_q_896</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -6582,7 +6656,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Amar jam gacer boyosh pray 3 year.gacer patha kishe jeno kheye felce.akshomoy puro patha kheye felce.akon ki korbo sir?</t>
+          <t>স্যার, আমি সিরাজগঞ্জের উল্লাপাড়ার বাসিন্দা। পড়াশোনা শেষ করে বাড়িতে ফলের চাষ শুরু করতে চাচ্ছি, তাই এ বিষয়ে ভালো কোনো প্রশিক্ষণের ব্যবস্থা বা সরকারি অনুদান পাওয়ার কোনো উপায় আছে কি না জানাবেন?</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -6594,21 +6668,21 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_899</t>
+          <t>farmer_q_302</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>লিচুর কলম করার নিয়মটা কি? বছরের কোন সময়ে কলম দিলে ভালো ফল পাওয়া যাবে?</t>
+          <t>শসা গাছের গোড়ায় পচন দেখা যাচ্ছে, আমি কি কোনো জৈব পদ্ধতি ব্যবহার করতে পারি?</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -6620,21 +6694,21 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_458</t>
+          <t>farmer_q_946</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>আমন ধানের সময় কোন সার আগে দিবো?</t>
+          <t>স্যার, আমার দেড় বিঘা আম্রপালি আর আধা বিঘা বারি-৪ বাগান আছে, এখন বাণিজ্যিকভাবে লাভবান হওয়ার জন্য আর কী কী জাতের আম লাগানো ভালো হবে? আমি একটু দ্বিধায় আছি, সঠিক পরামর্শ দিলে উপকৃত হতাম।</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -6646,11 +6720,11 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_148</t>
+          <t>farmer_q_15</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6660,7 +6734,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>সরিষা ক্ষেতে জাব পোকার আক্রমণ থেকে বাঁচার উপায় কী?</t>
+          <t>এখন কোন জাতের শিম চাষ করা যাবে সকলের পরামর্শ চাচ্ছি আর কোন কোম্পানির?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -6672,21 +6746,21 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_886</t>
+          <t>farmer_q_57</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>ভাই, আসসালামু আলাইকুম। আমার ৫০০০ খরের প্যাকেট (WS+PO2) আছে, কিন্তু মাশরুমের ফলন একদমই আশানুরূপ পাচ্ছি না। ফলন বাড়ানোর কোনো কার্যকর উপায় জানালে খুব উপকার হতো।</t>
+          <t>আসসালামু আলাইকুম সার হলুদের জমিতে আগাছা নাশক মারা জাবে কি?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -6698,11 +6772,11 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_951</t>
+          <t>farmer_q_309</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -6712,7 +6786,7 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>লাউ গাছে শুধু লতা বাড়ছে, কিন্তু ফুল তো ধরছে না। এটার সমাধান কী?</t>
+          <t>তরমুজ গাছের গোড়ায় পচন ধরে গাছ হঠাৎ শুকিয়ে যাচ্ছে, কী সমাধান?</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -6724,11 +6798,11 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_791</t>
+          <t>farmer_q_775</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -6738,7 +6812,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>দাদা, আমার কাজু গাছে প্রতি বছর মার্চ মাসে থোকায় থোকায় ফুল ফোটে, কিন্তু ফুলগুলো ঝরে যায়, কোনো ফল হয় না। গাছটার বয়স তো ১২ বছর হলো, এখন ফল না আসার কারণ কী হতে পারে?</t>
+          <t>দাদা, আমার টবের মরিচ গাছে ফুল তো প্রচুর আসে, কিন্তু একটাও মরিচ দাঁড়াচ্ছে না, সব ফুল ঝরে যাচ্ছে। এর কি কোনো উপায় আছে?</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -6750,25 +6824,21 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_678</t>
+          <t>farmer_q_834</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>সমস্যা সমুহ:-
-১.আম,ডালিম গাছে ফুল আসে কিন্তু ফল হয় না।তাছাড়াও ফুল ঝরে যায়।
-২.চীনা কমলার ফলন ভাল হয়,কিন্তু টক মিস্টি হই না।
-৩.কিছু কিছু গাছের পাতা হলুদ হয়ে যাচ্ছে।
-৪.কয়েকটি আম গাছে ফুল আসছে না।</t>
+          <t>আমি সিলেটে পেঁপে চাষ শুরু করতে চাচ্ছি, কোন জাতের পেঁপে দ্রুত ফলে আর বেশি ফলন দেয়? ভালো বীজ কোথা থেকে কিনবো? আর বীজতলা তৈরির পদ্ধতিসহ এক শতক জমিতে কতগুলো চারা রোপণ করা যায় তা জানাবেন।</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -6780,11 +6850,11 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_357</t>
+          <t>farmer_q_414</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -6794,7 +6864,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>বীজতলায় কি কোনো ভিটামিন দিতে হয়?</t>
+          <t>টমেটো গাছ হলুদ হয়ে যাচ্ছে কেন বুঝতে পারছি না, কি করবো?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -6806,21 +6876,21 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_183</t>
+          <t>farmer_q_338</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>ধানের পাতায় বাদামী রঙের দাগ পড়ছে, এটা কি রোগ এবং প্রতিকার কী?</t>
+          <t>ধানের পাতায় কেমন জানি লাল দাগ হইছে, কি করুম?</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -6832,21 +6902,21 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_445</t>
+          <t>farmer_q_125</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>সরষের খেতে হলুদ পোকা, কি করবো?</t>
+          <t>টমেটো গাছে ফল আসার পর ফল পচা শুরু হয়েছে, নিচের দিক থেকে কালো হয়ে যাচ্ছে। কী করব?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -6858,21 +6928,21 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_390</t>
+          <t>farmer_q_325</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>আলু গাছে মড়ক ধরলে এখন কি আর কোনো ওষুধ কাজ করবে?</t>
+          <t>বেগুন গাছের ডগা ও ফল ছিদ্রকারী পোকা দমনে জৈব বা নিরাপদ কোনো উপায় আছে কি?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -6884,21 +6954,21 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_593</t>
+          <t>farmer_q_216</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>লঙ্কা গাছে কুঁকড়ে যাওয়া রোগের কি কোনো ঘরোয়া সমাধান আছে?</t>
+          <t>শীতকালীন সবজির জন্য সার প্রয়োগের সঠিক নিয়ম কী?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -6910,11 +6980,11 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_150</t>
+          <t>farmer_q_135</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -6924,7 +6994,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>তরমুজ চাষে ভালো ফলন ও মিষ্টি স্বাদ পাওয়ার জন্য কোন সার কখন দেব?</t>
+          <t>বেগুন গাছে ডগা ও ফল ছিদ্রকারী পোকা দমনে জৈব পদ্ধতি কী?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -6936,11 +7006,11 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_696</t>
+          <t>farmer_q_63</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -6950,7 +7020,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>chad bagan korte koto khoroc hoy</t>
+          <t>আমন মৌসুমে সবচেয়ে উচ্চ ফলনশীল জাত কোনটি আমন মৌসুমে ৩৫ শতাংশ জমিতে আবাদ করতে চাই</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -6962,21 +7032,21 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_411</t>
+          <t>farmer_q_970</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>সরিষা ফুল আসার সময় কি সার দেওয়া লাগে?</t>
+          <t>ভাই, চিটাগাং শহরে লিটোসেন আর ডিএপি সার কোথায় পাওয়া যাবে একটু বলবেন?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -6988,11 +7058,11 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_567</t>
+          <t>farmer_q_470</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -7002,7 +7072,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>ঢ্যাঁড়স গাছে সাদা সাদা পোকা দেখা দিচ্ছে, কী করবো?</t>
+          <t>ধানের জমিতে প্রচুর আগাছা, কী ওষুধ মারলে ভালো হইবো?</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -7014,21 +7084,21 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_676</t>
+          <t>farmer_q_537</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>২০১৩ সালে প্রায় ২৫০ টি আকাশমনি গাছের চারা রোপন করি বর্গাকার পদ্ধতিতে। প্রতিটি চারার দুরত্ব প্রায় সাড়ে তিন হাত। বর্ষাকালের এক মাস বাগানে পানি অবস্থান করে। বর্তমানে পানি শুকিয়েছে। জমিতে প্রচুর পরিমানে আগাছা জন্মেছে। গাছগুলো আশারনুরুপ বড় হয়নি। গাছগুলোর কান্ড খুবই বাকা । কান্ড সুজা করা যাচ্ছে না। আমার পরামর্শ লাগবে কিভাবে দ্রুত বড় করা যায়। কখন কি কি সার, কিভাবে প্রয়োগ করতে হবে? ডালপালা ছেটে দিলে কখন কিভাবে কি পরিমান ছাটতে হবে? দয়া করে জানাবেন।</t>
+          <t>অকাল বৃষ্টিতে ধানের খুব ক্ষতি হইছে, এখন কি আর কিছু লাগানো যাবে?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -7039,7 +7109,628 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Treatment,Fertilizer,Prevention,General,Crisis,Off-Topic"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Query ID</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Source Channel</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Farmer Bengali Query (বাংলা প্রশ্ন)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Crop Name (বাংলায় ফসলের নাম)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Is Crop Specified? (ফসল আছে?)</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Intent Category (উদ্দেশ্য)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Confidence (আত্মবিশ্বাস)</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer Notes (মন্তব্য)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_349</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>ফল আসার আগে গাছ ঝিমিয়ে পড়ছে, কি করবো?</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="7" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr"/>
+    </row>
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="10" t="n">
+        <v>182</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_677</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>fb_group_real_farmer</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>আমার বাড়ীর ছাদে কিছু ফল গাছ অতি বৃষ্টি হওয়াতে
+কিছুটা দুরল হয়ে পরেছে।
+এই মুহুর্তে আমার করনিয় কি?</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_710</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>krishibangla.com</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Amar jam gacer boyosh pray 3 year.gacer patha kishe jeno kheye felce.akshomoy puro patha kheye felce.akon ki korbo sir?</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>184</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_899</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>krishibangla.com</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>লিচুর কলম করার নিয়মটা কি? বছরের কোন সময়ে কলম দিলে ভালো ফল পাওয়া যাবে?</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr"/>
+      <c r="F5" s="12" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="12" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_458</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>আমন ধানের সময় কোন সার আগে দিবো?</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="10" t="n">
+        <v>186</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_148</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>fb_group_real_farmer</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>সরিষা ক্ষেতে জাব পোকার আক্রমণ থেকে বাঁচার উপায় কী?</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_886</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>krishibangla.com</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ভাই, আসসালামু আলাইকুম। আমার ৫০০০ খরের প্যাকেট (WS+PO2) আছে, কিন্তু মাশরুমের ফলন একদমই আশানুরূপ পাচ্ছি না। ফলন বাড়ানোর কোনো কার্যকর উপায় জানালে খুব উপকার হতো।</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="10" t="n">
+        <v>188</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_951</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>fb_group_real_farmer</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>লাউ গাছে শুধু লতা বাড়ছে, কিন্তু ফুল তো ধরছে না। এটার সমাধান কী?</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="12" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_791</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>krishibangla.com</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>দাদা, আমার কাজু গাছে প্রতি বছর মার্চ মাসে থোকায় থোকায় ফুল ফোটে, কিন্তু ফুলগুলো ঝরে যায়, কোনো ফল হয় না। গাছটার বয়স তো ১২ বছর হলো, এখন ফল না আসার কারণ কী হতে পারে?</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_678</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>krishibangla.com</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>সমস্যা সমুহ:-
+১.আম,ডালিম গাছে ফুল আসে কিন্তু ফল হয় না।তাছাড়াও ফুল ঝরে যায়।
+২.চীনা কমলার ফলন ভাল হয়,কিন্তু টক মিস্টি হই না।
+৩.কিছু কিছু গাছের পাতা হলুদ হয়ে যাচ্ছে।
+৪.কয়েকটি আম গাছে ফুল আসছে না।</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_357</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>বীজতলায় কি কোনো ভিটামিন দিতে হয়?</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_183</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>fb_group_real_farmer</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>ধানের পাতায় বাদামী রঙের দাগ পড়ছে, এটা কি রোগ এবং প্রতিকার কী?</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_445</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>সরষের খেতে হলুদ পোকা, কি করবো?</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="10" t="n">
+        <v>194</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_390</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>আলু গাছে মড়ক ধরলে এখন কি আর কোনো ওষুধ কাজ করবে?</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_593</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>লঙ্কা গাছে কুঁকড়ে যাওয়া রোগের কি কোনো ঘরোয়া সমাধান আছে?</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="10" t="n">
+        <v>196</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_150</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>fb_group_real_farmer</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>তরমুজ চাষে ভালো ফলন ও মিষ্টি স্বাদ পাওয়ার জন্য কোন সার কখন দেব?</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="12" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_696</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>fb_group_real_farmer</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>chad bagan korte koto khoroc hoy</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_411</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>সরিষা ফুল আসার সময় কি সার দেওয়া লাগে?</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>farmer_q_567</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>field_sourced_farmer</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>ঢ্যাঁড়স গাছে সাদা সাদা পোকা দেখা দিচ্ছে, কী করবো?</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>farmer_q_676</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>krishibangla.com</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>২০১৩ সালে প্রায় ২৫০ টি আকাশমনি গাছের চারা রোপন করি বর্গাকার পদ্ধতিতে। প্রতিটি চারার দুরত্ব প্রায় সাড়ে তিন হাত। বর্ষাকালের এক মাস বাগানে পানি অবস্থান করে। বর্তমানে পানি শুকিয়েছে। জমিতে প্রচুর পরিমানে আগাছা জন্মেছে। গাছগুলো আশারনুরুপ বড় হয়নি। গাছগুলোর কান্ড খুবই বাকা । কান্ড সুজা করা যাচ্ছে না। আমার পরামর্শ লাগবে কিভাবে দ্রুত বড় করা যায়। কখন কি কি সার, কিভাবে প্রয়োগ করতে হবে? ডালপালা ছেটে দিলে কখন কিভাবে কি পরিমান ছাটতে হবে? দয়া করে জানাবেন।</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -7060,607 +7751,1251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>CONTROLLED TAXONOMY &amp; WORKED EXAMPLES (রেফারেন্স ও নমুনা উদাহরণ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>TABLE 1: CONTROLLED CROP VOCABULARY (ফসলের নিয়ন্ত্রিত তালিকা)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Crop Code (English Dropdown)</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Bangla Name (বাংলা নাম)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Botanical Family</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Common Aliases / Variety Names (আঞ্চলিক নাম ও জাত)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>কোনো ফসল নেই / অনুপস্থিত</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Missing / Underspecified</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>গাছের, পাতার, জমিতে, ইত্যাদি</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ধান</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Poaceae</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>আমন, বোরো, আউশ, ব্রি ধান</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>আলু</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Solanaceae</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>গোল আলু, ডায়মন্ড, কার্ডিনাল</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>wheat</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>গম</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Poaceae</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>বারি গম, গম ক্ষেত</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>corn</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>ভুট্টা</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Poaceae</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>ভুট্টা, হাইব্রিড ভুট্টা</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>টমেটো</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Solanaceae</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>টমেটো, বিলাতি বেগুন</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>chilli</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>মরিচ</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Solanaceae</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>মরিচ, কাঁচা মরিচ, লঙ্কা</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>brinjal</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>বেগুন</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Solanaceae</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>বেগুন, তাল বেগুন</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>mustard</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>সরিষা</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>সরিষা, টরি, রাই</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>আম</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Anacardiaceae</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>আম, হিমসাগর, ল্যাংড়া, ফজলি</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>papaya</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>পেঁপে</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Caricaceae</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>পেঁপে, পেপে</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>banana</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>কলা</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Musaceae</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>কলা, সাগর কলা, সবরি কলা</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>guava</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>পেয়ারা</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Myrtaceae</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>পেয়ারা, কাজী পেয়ারা</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>lemon</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>লেবু</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Rutaceae</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>লেবু, কাগজি লেবু, বাতাবি লেবু</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>তরমুজ</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>তরমুজ, তরমুজের লতা</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>coconut</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>নারিকেল</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Arecaceae</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>নারিকেল, নারিকেল গাছ, ডাব</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>jackfruit</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>কাঁঠাল</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>কাঁঠাল, কাঁঠাল গাছ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>শসা</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>শসা, শশা</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>bottle_gourd</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>লাউ</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>লাউ, কদু</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>bitter_gourd</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>করলা</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>করলা, উচ্ছে</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>বাঁধাকপি</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>বাঁধাকপি, পাতাকপি</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>cauliflower</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>ফুলকপি</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>ফুলকপি</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>jute</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>পাট</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Malvaceae</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>পাট, তোষা পাট, দেশী পাট</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>onion</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>পেঁয়াজ</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Amaryllidaceae</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>পেঁয়াজ, পেয়াজ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>রসুন</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Amaryllidaceae</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>রসুন</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>ginger</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>আদা</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Zingiberaceae</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>আদা</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>turmeric</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>হলুদ</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>Zingiberaceae</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>হলুদ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>betel_leaf</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>পান</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Piperaceae</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>পান, পানের বরজ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>চা</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>Theaceae</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>চা, চা বাগান</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>mushroom</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>মাশরুম</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Fungi</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>মাশরুম</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>strawberry</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>স্ট্রবেরি</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>Rosaceae</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>স্ট্রবেরি</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>dragon_fruit</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>ড্রাগন ফল</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Cactaceae</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>ড্রাগন ফল, ড্রাগন গাছ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>litchi</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>লিচু</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>Sapindaceae</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>লিচু, বোম্বাই লিচু</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>pointed_gourd</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>পটল</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>পটল</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>okra</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>ঢেঁড়শ</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Malvaceae</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>ঢেঁড়শ, ভেন্ডি</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>bean</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>শিম</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Fabaceae</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>শিম, সীম</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>other_crop</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>অন্যান্য ফসল</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>অন্য কোনো নির্দিষ্ট ফসল</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>TABLE 2: INTENT CATEGORY TAXONOMY (প্রশ্নের ধরণ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Intent Code (Dropdown)</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Bangla Description (বাংলা অর্থ)</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Typical Scope &amp; Trigger Keywords (লক্ষণ ও মূল শব্দ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>রোগ বা পোকার প্রতিকার</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>কীটনাশক, বালাইনাশক, রোগ লক্ষণ, স্প্রে, ওষুধ, বিষ, পোকা দমন</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>Fertilizer</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>সার ব্যবস্থাপনা ও মাত্রা</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>ইউরিয়া, টিএসপি, ডিএপি, পটাশ, জিংক, সারের মাত্রা, প্রয়োগ সময়</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Prevention</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>রোগ প্রতিরোধ ও শোধন</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>বীজ শোধন, বালাই প্রতিরোধ, পূর্বপ্রস্তুতিমূলক স্প্রে</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>সাধারণ কৃষি পরামর্শ</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>চাষ পদ্ধতি, বীজ বপন, জাত নির্বাচন, সেচ, জমি তৈরি, ফসল তোলার সময়</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Crisis</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>জরুরি বিষক্রিয়া / নিষিদ্ধ রাসায়নিক</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>কীটনাশক খেয়ে ফেলা, চোখে/মুখে বিষ লাগা, প্যারাকোয়াট, ফিউরাডন</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>Off-Topic</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>অকৃষি প্রশ্ন / অপ্রাসঙ্গিক</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>রাজনীতি, বিনোদন, সাধারণ প্রশ্ন, আবোল-তাবোল</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>TABLE 3: WORKED EXAMPLES (নমুনা পূর্ণাঙ্গ এ্যানোটেশন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>Item #</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Query ID</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Source Channel</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Farmer Bengali Query (বাংলা প্রশ্ন)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Crop Name (বাংলায় ফসলের নাম)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Crop Taxonomy (English)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Is Crop Specified? (ফসল আছে?)</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Intent Category (উদ্দেশ্য)</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Confidence (আত্মবিশ্বাস)</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Reviewer Notes (মন্তব্য)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="54" customHeight="1">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_136</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>আলুর জমিতে লেট ব্লাইট বা মড়ক রোগ থেকে বাঁচার উপায় কী?</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr"/>
-      <c r="F2" s="7" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="7" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
-    </row>
-    <row r="3" ht="54" customHeight="1">
-      <c r="A3" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_856</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>krishibangla.com</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>ভাই, অতিরিক্ত বৃষ্টির কারণে আমার ছাদের ফলের গাছগুলো কেমন যেন ঝিমিয়ে গেছে আর দুর্বল হয়ে পড়ছে। এখন আমি কী করতে পারি?</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr"/>
-      <c r="F3" s="12" t="inlineStr"/>
-      <c r="G3" s="10" t="inlineStr"/>
-      <c r="H3" s="12" t="inlineStr"/>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="14" t="inlineStr"/>
-    </row>
-    <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_748</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>আতা গাছে প্রচুর ফুল আসে কিন্তু ঝরে যায়, কী করলে ফুলগুলো টিকবে আর ফল হবে?</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="7" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_51</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>আমের ভিতরে পোকা মারার জন্য কোন বিষ স্পে করতে হবে?</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr"/>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="14" t="inlineStr"/>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_258</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>আম গাছে ছত্রাক বা পাউডারি মিলডিউ রোগের প্রকোপ বাড়ছে। ঘরোয়া বা ভালো কোনো সমাধান আছে কি?</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_332</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>ধানের চারাগাছ লাল হয়ে যাচ্ছে, কি কোনো সারের ঘাটতি?</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_81</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>সলুবোর + কুইকপটাশ +চিলেটেড জিংক 
-একসাথে মিশিয়ে স্প্রে করা যাবে?</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_607</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>field_sourced_farmer</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>আমন ধানের জমিতে কি এখন পটাশ সার দেওয়া যাবে?</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_282</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>পেঁপে গাছের গোড়া পচা রোধে কী করণীয়?</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_389</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>field_sourced_farmer</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>ফসলের মাঠ খুব শুকনা, কতদিন পর পর পানি দিমু?</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr"/>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr"/>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_413</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>field_sourced_farmer</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>ধানের পাতায় কেমন জানি লাল দাগ হইছে, কি ঔষধ দিমু?</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_49</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>"আমাদের আম গাছের ফলগুলো এই বছর এরকম বাদামী-কালো দাগযুক্ত, কুঁচকে যাওয়া এবং অনেক ফল ঝরে পড়ছে (ছবি সংযুক্ত)। এটা কোন রোগ হতে পারে? বিশেষ করে এনথ্রাকনোজ নাকি অন্য কিছু?
-এর প্রতিকার কি?</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr"/>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_311</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>কলা গাছের পাতা হলুদ হয়ে ঝুলে পড়ছে, গোড়া থেকে কালো দাগ আসছে। করণীয় কী?</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_174</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>টমেটো গাছে পাতা মোড়ানো রোগ হয়েছে, গাছগুলো একদম কুঁকড়ে গেছে। প্রতিকার কী?</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr"/>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_83</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>পাটের জমিতে শুধু কিউলোপ দিছি এতে কি কাজ হবে?</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_110</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>শীতকালীন শাকসবজি চাষে হরমোন কি ব্যবহার করা ঠিক?</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr"/>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_468</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>field_sourced_farmer</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>মাটি খুব শক্ত হয়ে গেছে, আবাদ কি ভালো হবে?</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_112</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>সবজির পাতায় সাদা রঙের মাকড়সার মতো কী যেন দেখা যাচ্ছে, গাছ বিবর্ণ হয়ে যাচ্ছে?</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr"/>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="14" t="inlineStr"/>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>farmer_q_44</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>fb_group_real_farmer</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>ভালো জাতের লাউ বীজ সাজেস্ট করেন প্লিজ, যেগুলা রোগপ্রতিরোধী এবং অধিক ফলশীন!</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>farmer_q_841</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>krishibangla.com</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>গ্ল্যাডিওলাস লাগানোর সময় টিএসপি সার দিতে ভুলে গিয়েছিলাম, বাকি সব সার দেওয়া হয়েছে। এখন এই অবস্থায় টিএসপি সারটা কীভাবে প্রয়োগ করলে ভালো হয়?</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr"/>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="14" t="inlineStr"/>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Query (বাংলা প্রশ্ন)</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Crop (বাংলা)</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Crop (English)</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>Specified?</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>Intent</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t>Notes / Explanation (মন্তব্য ও যুক্তি)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>EX-01</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>sample_q_01</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>ধানের পাতায় বাদামি দাগ দেখা যাচ্ছে এবং পাতা শুকিয়ে যাচ্ছে। এখন কি ওষুধ স্প্রে করব?</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>ধান</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G56" s="28" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="H56" s="25" t="inlineStr">
+        <is>
+          <t>স্পষ্টভাবে ধানের নাম এবং ব্লাইট রোগের প্রতিকার চাওয়া হয়েছে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>EX-02</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>sample_q_02</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>গাছের ডাল পচে যাচ্ছে এবং পাতা হলুদ হচ্ছে, ভালো একটা ছত্রাকনাশকের নাম বলেন।</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>কোনো ফসল নেই</t>
+        </is>
+      </c>
+      <c r="E57" s="26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" s="28" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="inlineStr">
+        <is>
+          <t>অস্পষ্ট/ফসলহীন: গাছের উল্লেখ আছে কিন্তু কিসের গাছ (আলু/টমেটো/বেগুন) বলা নেই। রাসায়নিক পরামর্শ দেওয়া বিপজ্জনক।</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>EX-03</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>sample_q_03</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>আলু লাগানোর কত দিন পর প্রথম ইউরিয়া ও পটাশ সার উপরিপ্রয়োগ করতে হয়?</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>আলু</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G58" s="28" t="inlineStr">
+        <is>
+          <t>Fertilizer</t>
+        </is>
+      </c>
+      <c r="H58" s="25" t="inlineStr">
+        <is>
+          <t>নির্দিষ্ট ফসল (আলু) এবং সার প্রয়োগের সময়সূচী জানতে চাওয়া হয়েছে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>EX-04</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>sample_q_04</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>মাজরা পোকার আক্রমণে কুশি শুকিয়ে যাচ্ছে, কি বিষ দিলে ভালো ফল পাব?</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>কোনো ফসল নেই</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" s="28" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr">
+        <is>
+          <t>লক্ষণভিত্তিক কিন্তু ফসল অনুপস্থিত: মাজরা পোকা মূলত ধানে হলেও ভুট্টা বা আখ গাছেও হয়। ফসল নিশ্চিত না হয়ে কীটনাশক দেওয়া অনিরাপদ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>EX-05</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>sample_q_05</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>স্প্রে করার সময় মুখে কীটনাশক ঢুকে বমি ও মাথা ঘোরা শুরু হয়েছে, এখন কি করণীয়?</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>কোনো ফসল নেই</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G60" s="28" t="inlineStr">
+        <is>
+          <t>Crisis</t>
+        </is>
+      </c>
+      <c r="H60" s="25" t="inlineStr">
+        <is>
+          <t>জরুরি বিষক্রিয়ার ঘটনা: তাৎক্ষণিক ১৬১২৩ / ৯৯৯ বা হাসপাতালে রেফার করতে হবে।</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"YES,NO"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Treatment,Fertilizer,Prevention,General,Crisis,Off-Topic"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7679,7 +9014,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -7714,7 +9049,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -7740,21 +9075,21 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_379</t>
+          <t>farmer_q_136</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>ধানের জমিতে ইউরিয়া সার কতটুকু দেওয়া উচিত?</t>
+          <t>আলুর জমিতে লেট ব্লাইট বা মড়ক রোগ থেকে বাঁচার উপায় কী?</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -7766,21 +9101,21 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_186</t>
+          <t>farmer_q_856</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>বর্ষাকালে মরিচ গাছে গোড়া পচা রোগ থেকে বাঁচার উপায় কী?</t>
+          <t>ভাই, অতিরিক্ত বৃষ্টির কারণে আমার ছাদের ফলের গাছগুলো কেমন যেন ঝিমিয়ে গেছে আর দুর্বল হয়ে পড়ছে। এখন আমি কী করতে পারি?</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -7792,11 +9127,11 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_701</t>
+          <t>farmer_q_748</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -7806,7 +9141,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>strawberry chas shomporke jante cai</t>
+          <t>আতা গাছে প্রচুর ফুল আসে কিন্তু ঝরে যায়, কী করলে ফুলগুলো টিকবে আর ফল হবে?</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -7818,21 +9153,21 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_552</t>
+          <t>farmer_q_51</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>ভুইতে জল দিলে গাছ হলুদ হইয়া যায়, কি করব?</t>
+          <t>আমের ভিতরে পোকা মারার জন্য কোন বিষ স্পে করতে হবে?</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -7844,21 +9179,21 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_471</t>
+          <t>farmer_q_258</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>ফুলকপি বড় হচ্ছে না, কী খৈল বা সার দিমু?</t>
+          <t>আম গাছে ছত্রাক বা পাউডারি মিলডিউ রোগের প্রকোপ বাড়ছে। ঘরোয়া বা ভালো কোনো সমাধান আছে কি?</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -7870,11 +9205,11 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_301</t>
+          <t>farmer_q_332</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -7884,7 +9219,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>সরিষা ক্ষেতে জাব পোকার আক্রমণ থেকে মুক্তি পাওয়ার উপায় কী?</t>
+          <t>ধানের চারাগাছ লাল হয়ে যাচ্ছে, কি কোনো সারের ঘাটতি?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -7896,11 +9231,11 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_176</t>
+          <t>farmer_q_81</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -7910,7 +9245,8 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>তরমুজ চাষের জন্য ভালো কোনো হাইব্রিড জাতের নাম বলবেন কি?</t>
+          <t>সলুবোর + কুইকপটাশ +চিলেটেড জিংক 
+একসাথে মিশিয়ে স্প্রে করা যাবে?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -7922,21 +9258,21 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_116</t>
+          <t>farmer_q_607</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>পেঁপে গাছের পাতা কুকড়ে যাচ্ছে, এটি কি কোনো পোকার আক্রমণ?</t>
+          <t>আমন ধানের জমিতে কি এখন পটাশ সার দেওয়া যাবে?</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -7948,21 +9284,21 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_930</t>
+          <t>farmer_q_282</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>স্ট্রবেরি চাষ করতে কী কী লাগে আর এর পরিচর্যা কীভাবে করতে হয়?</t>
+          <t>পেঁপে গাছের গোড়া পচা রোধে কী করণীয়?</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -7974,11 +9310,11 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_620</t>
+          <t>farmer_q_389</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -7988,7 +9324,7 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>শসা গাছে ফুল আসছে কিন্তু ঝরে যাচ্ছে, কী করি?</t>
+          <t>ফসলের মাঠ খুব শুকনা, কতদিন পর পর পানি দিমু?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -8000,21 +9336,21 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_189</t>
+          <t>farmer_q_413</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>ধানের জমিতে ইউরিয়া সারের অপচয় কমাতে করণীয় কী?</t>
+          <t>ধানের পাতায় কেমন জানি লাল দাগ হইছে, কি ঔষধ দিমু?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -8026,11 +9362,11 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_23</t>
+          <t>farmer_q_49</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -8040,8 +9376,8 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>লাউ, করলা, ধুন্দল, চালকুমড়া
-এই মাসে (জুন) এগুলোর মধ্যে কোনটা কোনটা চাষ করলে বেশি ভালো হবে?</t>
+          <t>"আমাদের আম গাছের ফলগুলো এই বছর এরকম বাদামী-কালো দাগযুক্ত, কুঁচকে যাওয়া এবং অনেক ফল ঝরে পড়ছে (ছবি সংযুক্ত)। এটা কোন রোগ হতে পারে? বিশেষ করে এনথ্রাকনোজ নাকি অন্য কিছু?
+এর প্রতিকার কি?</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -8053,21 +9389,21 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_998</t>
+          <t>farmer_q_311</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>বাঁশের গোড়ায় মাটি দেওয়ার পর কোন সার ব্যবহার করলে বাঁশ মোটা আর বেশি হবে, সেটা জানতে চাচ্ছিলাম।</t>
+          <t>কলা গাছের পাতা হলুদ হয়ে ঝুলে পড়ছে, গোড়া থেকে কালো দাগ আসছে। করণীয় কী?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -8079,11 +9415,11 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_933</t>
+          <t>farmer_q_174</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -8093,7 +9429,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>আমাদের পত্নীতলার জমিতে মাল্টা বা বেদানার বাগান করা কি ঠিক হবে? জমিটা এতদিন খালি পড়ে ছিল, এখন এখানে চাষ করার জন্য ভালো জাতের পরামর্শ দিলে খুব উপকার হতো।</t>
+          <t>টমেটো গাছে পাতা মোড়ানো রোগ হয়েছে, গাছগুলো একদম কুঁকড়ে গেছে। প্রতিকার কী?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -8105,11 +9441,11 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_140</t>
+          <t>farmer_q_83</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -8119,7 +9455,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>পেঁপে গাছের কান্ডে পচন দেখা দিচ্ছে, কী ঔষধ দিব?</t>
+          <t>পাটের জমিতে শুধু কিউলোপ দিছি এতে কি কাজ হবে?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -8131,11 +9467,11 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_964</t>
+          <t>farmer_q_110</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -8145,7 +9481,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>বেগুনের ডগার পোকা সব নষ্ট করে দিচ্ছে, ডগাগুলো ঝুলে মরে যাচ্ছে। এর কি কোনো ওষুধ আছে?</t>
+          <t>শীতকালীন শাকসবজি চাষে হরমোন কি ব্যবহার করা ঠিক?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -8157,21 +9493,21 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_700</t>
+          <t>farmer_q_468</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>আমি ছাদে বাগান করার বিষয়ে আগ্রহী। কিভাবে ছাদে বাগান করার কৌশল জানতে পারবো দয়া করে জানাবেন।</t>
+          <t>মাটি খুব শক্ত হয়ে গেছে, আবাদ কি ভালো হবে?</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -8183,11 +9519,11 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_232</t>
+          <t>farmer_q_112</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -8197,7 +9533,7 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>বর্ষাকালের লাউ বা মিষ্টি কুমড়া চাষে গোড়া পচা রোধে কী করণীয়?</t>
+          <t>সবজির পাতায় সাদা রঙের মাকড়সার মতো কী যেন দেখা যাচ্ছে, গাছ বিবর্ণ হয়ে যাচ্ছে?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -8209,11 +9545,11 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_98</t>
+          <t>farmer_q_44</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -8223,7 +9559,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>তীব্র রোধে বারি ৪ আমের পোড়া দাগ রোধে কী করবো?</t>
+          <t>ভালো জাতের লাউ বীজ সাজেস্ট করেন প্লিজ, যেগুলা রোগপ্রতিরোধী এবং অধিক ফলশীন!</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -8235,11 +9571,11 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_860</t>
+          <t>farmer_q_841</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -8249,7 +9585,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>আমার বাগানের আম-ডালিম গাছে ফুল ঝরে যাচ্ছে আর কিছু গাছে তো ফুলই আসছে না। এছাড়া কমলার স্বাদ টক-মিষ্টি হচ্ছে না এবং গাছের পাতাও হলুদ হয়ে যাচ্ছে, এর কোনো সমাধান আছে কি?</t>
+          <t>গ্ল্যাডিওলাস লাগানোর সময় টিএসপি সার দিতে ভুলে গিয়েছিলাম, বাকি সব সার দেওয়া হয়েছে। এখন এই অবস্থায় টিএসপি সারটা কীভাবে প্রয়োগ করলে ভালো হয়?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -8260,7 +9596,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -8289,7 +9628,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -8324,7 +9663,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -8350,21 +9689,21 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_917</t>
+          <t>farmer_q_379</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>টবের মাটিতে প্রচুর পিঁপড়া ধরেছে, গাছের ক্ষতি না করে কীভাবে এদের দূর করা যায় একটু জানাবেন?</t>
+          <t>ধানের জমিতে ইউরিয়া সার কতটুকু দেওয়া উচিত?</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -8376,21 +9715,21 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_698</t>
+          <t>farmer_q_186</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>মাশরুম চাষ করতে চাই,এবং চাষের পদ্ধিতি জানতে চাই</t>
+          <t>বর্ষাকালে মরিচ গাছে গোড়া পচা রোগ থেকে বাঁচার উপায় কী?</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -8402,11 +9741,11 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_79</t>
+          <t>farmer_q_701</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -8416,9 +9755,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>বাতির স্প্রে করার পরও
-ঘাসের কচি পাতা খাওয়া পোকা (ফল আর্মি ওয়ার্ম) দমন হচ্ছে না।
-করণীয়?</t>
+          <t>strawberry chas shomporke jante cai</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -8430,21 +9767,21 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_982</t>
+          <t>farmer_q_552</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>শুনলাম নরসিংদী থেকে এখন বিদেশে লেবু পাঠাচ্ছে। আমি আমার বাগানের লেবু তাদের কাছে বিক্রি করতে চাই, কিন্তু কীভাবে যোগাযোগ করব বা কার সাথে কথা বলব বুঝতে পারছি না।</t>
+          <t>ভুইতে জল দিলে গাছ হলুদ হইয়া যায়, কি করব?</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -8456,11 +9793,11 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_585</t>
+          <t>farmer_q_471</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -8470,7 +9807,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>জমিতে কি এখন गोबर সার দেওয়া যাবে নাকি দেরি আছে?</t>
+          <t>ফুলকপি বড় হচ্ছে না, কী খৈল বা সার দিমু?</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -8482,21 +9819,21 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_719</t>
+          <t>farmer_q_301</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>নরসিংদী হতে ইদানিং বিদেশে লেবু রপ্তানী করা হচ্ছে কিন্তু তাদের সাথে কি ভাবে যোগাযোগ করিব? দয়া করে জানাবেন কি? কোন ফোন নম্বর অথবা ইমেই নম্বর দিতে পারিবেন কি?</t>
+          <t>সরিষা ক্ষেতে জাব পোকার আক্রমণ থেকে মুক্তি পাওয়ার উপায় কী?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -8508,21 +9845,21 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_494</t>
+          <t>farmer_q_176</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>পেপে গাছের পাতা কোঁকড়ে যাচ্ছে, কী রোগ এটা?</t>
+          <t>তরমুজ চাষের জন্য ভালো কোনো হাইব্রিড জাতের নাম বলবেন কি?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -8534,11 +9871,11 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_661</t>
+          <t>farmer_q_116</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -8548,7 +9885,7 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>এক জাতের পোকা নারকেল গাছে  পাতা খেয়ে ফেলছে।কি করনীয়। কিভাবে নারকেলের ফলন বাড়ানো যায়।</t>
+          <t>পেঁপে গাছের পাতা কুকড়ে যাচ্ছে, এটি কি কোনো পোকার আক্রমণ?</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -8560,21 +9897,21 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_107</t>
+          <t>farmer_q_930</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>পেয়ারা গাছের পাতা কুঁকড়ে যাচ্ছে, কী পোকা হতে পারে?</t>
+          <t>স্ট্রবেরি চাষ করতে কী কী লাগে আর এর পরিচর্যা কীভাবে করতে হয়?</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -8586,11 +9923,11 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_406</t>
+          <t>farmer_q_620</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -8600,7 +9937,7 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>সরিষার ফুল আসতেছে, এখন কি আর জল দিমু জমিতে?</t>
+          <t>শসা গাছে ফুল আসছে কিন্তু ঝরে যাচ্ছে, কী করি?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -8612,21 +9949,21 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_660</t>
+          <t>farmer_q_189</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>আমি ছাদে বাগান করি। প্রশিক্ষণ চাই।</t>
+          <t>ধানের জমিতে ইউরিয়া সারের অপচয় কমাতে করণীয় কী?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -8638,11 +9975,11 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_101</t>
+          <t>farmer_q_23</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -8652,8 +9989,8 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>সলুবোর + কুইকপটাশ +চিলেটেড জিংক 
-একসাথে মিশিয়ে স্প্রে করা যাবে?</t>
+          <t>লাউ, করলা, ধুন্দল, চালকুমড়া
+এই মাসে (জুন) এগুলোর মধ্যে কোনটা কোনটা চাষ করলে বেশি ভালো হবে?</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -8665,11 +10002,11 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_985</t>
+          <t>farmer_q_998</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -8679,7 +10016,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>আমার গোলাপ গাছের নতুন কুঁড়িগুলো সব কুঁকড়ে যাচ্ছে আর পাতা ও ফুলে কালো দাগ পড়ছে। ফুলগুলোও ঠিকমতো ফুটছে না, ছোট হয়ে ঝরে যাচ্ছে; এখন কী করলে গাছটা বাঁচবে?</t>
+          <t>বাঁশের গোড়ায় মাটি দেওয়ার পর কোন সার ব্যবহার করলে বাঁশ মোটা আর বেশি হবে, সেটা জানতে চাচ্ছিলাম।</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -8691,11 +10028,11 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_769</t>
+          <t>farmer_q_933</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -8705,7 +10042,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>নারকেল গাছে বড় কালো রঙের শক্ত পোকা ধরেছে, গাছের মাথায় প্রায় ২ সেন্টিমিটারের মতো গর্ত করে ফেলেছে। গাছ বাঁচানোর উপায় কী?</t>
+          <t>আমাদের পত্নীতলার জমিতে মাল্টা বা বেদানার বাগান করা কি ঠিক হবে? জমিটা এতদিন খালি পড়ে ছিল, এখন এখানে চাষ করার জন্য ভালো জাতের পরামর্শ দিলে খুব উপকার হতো।</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -8717,11 +10054,11 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_12</t>
+          <t>farmer_q_140</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -8731,7 +10068,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>৩৩ শতাংশ জমিতে ঢেঁড়সের বীজ কতটুকু লাগবে?</t>
+          <t>পেঁপে গাছের কান্ডে পচন দেখা দিচ্ছে, কী ঔষধ দিব?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -8743,11 +10080,11 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_3</t>
+          <t>farmer_q_964</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -8757,7 +10094,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>আম গাছে আমের গোড়ায় এমন সাদা কালো দাগ এ অবস্থায় কি করা যায়?</t>
+          <t>বেগুনের ডগার পোকা সব নষ্ট করে দিচ্ছে, ডগাগুলো ঝুলে মরে যাচ্ছে। এর কি কোনো ওষুধ আছে?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -8769,21 +10106,21 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_702</t>
+          <t>farmer_q_700</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Sir can i commercially planted mata or bedana on our land. ( Patnitola, Naogaon) un fartil land. what type is good. pls sujjest.</t>
+          <t>আমি ছাদে বাগান করার বিষয়ে আগ্রহী। কিভাবে ছাদে বাগান করার কৌশল জানতে পারবো দয়া করে জানাবেন।</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -8795,21 +10132,21 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_403</t>
+          <t>farmer_q_232</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>ধানের ক্ষেতে ইঁদুরের উপদ্রব খুব, কি করুম?</t>
+          <t>বর্ষাকালের লাউ বা মিষ্টি কুমড়া চাষে গোড়া পচা রোধে কী করণীয়?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -8821,21 +10158,21 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_857</t>
+          <t>farmer_q_98</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>টানা বৃষ্টির চোটে ছাদের গাছগুলো একদম নেতিয়ে গেছে, ডালপালাও খুব দুর্বল দেখাচ্ছে। এখন গাছের যত্ন নিতে কী কী করা দরকার?</t>
+          <t>তীব্র রোধে বারি ৪ আমের পোড়া দাগ রোধে কী করবো?</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -8847,21 +10184,21 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_441</t>
+          <t>farmer_q_860</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>আলু গাছে কালো দাগ পড়তেছে, এটা কি পচন রোগ?</t>
+          <t>আমার বাগানের আম-ডালিম গাছে ফুল ঝরে যাচ্ছে আর কিছু গাছে তো ফুলই আসছে না। এছাড়া কমলার স্বাদ টক-মিষ্টি হচ্ছে না এবং গাছের পাতাও হলুদ হয়ে যাচ্ছে, এর কোনো সমাধান আছে কি?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -8872,7 +10209,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -8901,7 +10241,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -8936,7 +10276,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -8962,21 +10302,21 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_483</t>
+          <t>farmer_q_917</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>বেগুনের ডগা পচা রোগ হইছে, কি করমু বুঝতেছি না</t>
+          <t>টবের মাটিতে প্রচুর পিঁপড়া ধরেছে, গাছের ক্ষতি না করে কীভাবে এদের দূর করা যায় একটু জানাবেন?</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -8988,11 +10328,11 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_640</t>
+          <t>farmer_q_698</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -9002,13 +10342,7 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>আমি আমার বাড়ীর পাশে কিছু সংখ্যক কাঠালের চারা রুপন করি গত ৩-৪ বছর আগে।
-বিগত কয়েক বছর ধরে প্রায় সব গাছেই কাঠাল আসছে। কিন্তু আমার একটি গাছের কাঠাল পচে ঝরে যায়।
-পচার ধরন -বাইরে থেকে বুঝা যায় না , যখন কাঠাল পরিপক্ক হয় বা খাওয়ার উপযোগি হই তখন গাছ থেকে পেড়ে নিই।
-বড়ই দুঃখের বিষয় এই যে পাকার জন্য রেখে দিলে পরে দেখা যাই মুলি(মুল দন্ড যার চার পাশে কোষ থাকে) পচে যায় ও কাঠালে দুর্ঘ্নদ সৃস্টি হয় ফলে খাওার উপযোগি থাকেনা।
-ভেবে ছিলাম আমাদের পাকানোর কোন ভুল তাই পরবর্তি বছর মানে এই মৌসোম এ কাঠাল গাছে পাকানোর সিদ্ধান্ত নিই ।কিন্তু
-যখন দেখতে পেলাম কাঠাল গাছেই পূর্বে বর্ণিত অবস্থায় পচে যাচ্ছে তখন খুভই মর্মাহত হলাম।
-আমি এর সঠিক সমাধান চাই। ধন্যবাদ</t>
+          <t>মাশরুম চাষ করতে চাই,এবং চাষের পদ্ধিতি জানতে চাই</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -9020,23 +10354,23 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_667</t>
+          <t>farmer_q_79</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>আম গাছের বৃদ্ধি হয়না ও ফুল ধরে না। গাছের বয়স ৭-৮ বছর।
-এখন কি ধরনের সার দিতে হবে?
-ধন্যবাদ।।</t>
+          <t>বাতির স্প্রে করার পরও
+ঘাসের কচি পাতা খাওয়া পোকা (ফল আর্মি ওয়ার্ম) দমন হচ্ছে না।
+করণীয়?</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -9048,21 +10382,21 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_528</t>
+          <t>farmer_q_982</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>কলা গাছের গোড়ায় কি যেন লালচে দাগ, এটা কি রোগ?</t>
+          <t>শুনলাম নরসিংদী থেকে এখন বিদেশে লেবু পাঠাচ্ছে। আমি আমার বাগানের লেবু তাদের কাছে বিক্রি করতে চাই, কিন্তু কীভাবে যোগাযোগ করব বা কার সাথে কথা বলব বুঝতে পারছি না।</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -9074,21 +10408,21 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_321</t>
+          <t>farmer_q_585</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>গম চাষে আগাছা দমনে কি করব?</t>
+          <t>জমিতে কি এখন गोबर সার দেওয়া যাবে নাকি দেরি আছে?</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -9100,11 +10434,11 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_634</t>
+          <t>farmer_q_719</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -9114,7 +10448,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>angor geser pata bindo bindo hoea pataer majkan shokea jea.porea pata jora jea.pls help me. sir.</t>
+          <t>নরসিংদী হতে ইদানিং বিদেশে লেবু রপ্তানী করা হচ্ছে কিন্তু তাদের সাথে কি ভাবে যোগাযোগ করিব? দয়া করে জানাবেন কি? কোন ফোন নম্বর অথবা ইমেই নম্বর দিতে পারিবেন কি?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -9126,11 +10460,11 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_507</t>
+          <t>farmer_q_494</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -9140,7 +10474,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>কলা গাছে কি যেন কালো দাগ হইছে, গাছটা কি কাইটা ফেলমু?</t>
+          <t>পেপে গাছের পাতা কোঁকড়ে যাচ্ছে, কী রোগ এটা?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -9152,11 +10486,11 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_668</t>
+          <t>farmer_q_661</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -9166,7 +10500,7 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>about good papaw seet  where</t>
+          <t>এক জাতের পোকা নারকেল গাছে  পাতা খেয়ে ফেলছে।কি করনীয়। কিভাবে নারকেলের ফলন বাড়ানো যায়।</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -9178,11 +10512,11 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_40</t>
+          <t>farmer_q_107</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -9192,7 +10526,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>জমি দুবলা ঘাসে চেপে গেছে। এই ঘাস হাল চাষের পূর্বেই নির্মূল করতে (পুড়িয়ে ফেলতে) কোন ওষুধ স্প্রে করলে ভালো ফলাফল পাওয়া যাবে?</t>
+          <t>পেয়ারা গাছের পাতা কুঁকড়ে যাচ্ছে, কী পোকা হতে পারে?</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -9204,21 +10538,21 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_648</t>
+          <t>farmer_q_406</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>নারকেল গাছে একধরনের বড় বিটল জাতীয় পোকা গাছ খেয়ে ফেলছে।পোকা দেখতে কালো ও শক্ত আবরন।পোকার গর্তের পরিধি আনুমানিক 2cm প্রায়। করনীয় কি।</t>
+          <t>সরিষার ফুল আসতেছে, এখন কি আর জল দিমু জমিতে?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -9230,21 +10564,21 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_111</t>
+          <t>farmer_q_660</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>আলুর নাভি ধসা রোগ থেকে বাঁচতে কী করণীয়?</t>
+          <t>আমি ছাদে বাগান করি। প্রশিক্ষণ চাই।</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -9256,21 +10590,22 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_840</t>
+          <t>farmer_q_101</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>মুরগির বাচ্চার স্বাস্থ্য ভালো রাখতে প্রাকৃতিক প্রোবায়োটিক হিসেবে কী খাওয়ানো ভালো? এমন কিছু খুঁজছি যাতে বাচ্চার পেটে উপকারী ব্যাকটেরিয়া বাড়ে।</t>
+          <t>সলুবোর + কুইকপটাশ +চিলেটেড জিংক 
+একসাথে মিশিয়ে স্প্রে করা যাবে?</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -9282,21 +10617,21 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_193</t>
+          <t>farmer_q_985</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>বেগুন গাছের গোড়া পচে যাচ্ছে এবং গাছ ঝিমিয়ে পড়ছে। কোন ছত্রাকনাশক ব্যবহার করলে ভালো ফল পাব?</t>
+          <t>আমার গোলাপ গাছের নতুন কুঁড়িগুলো সব কুঁকড়ে যাচ্ছে আর পাতা ও ফুলে কালো দাগ পড়ছে। ফুলগুলোও ঠিকমতো ফুটছে না, ছোট হয়ে ঝরে যাচ্ছে; এখন কী করলে গাছটা বাঁচবে?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -9308,21 +10643,21 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_420</t>
+          <t>farmer_q_769</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>জমিতে আগাছা বেশি হইয়া গেছে, ওষুধ দিয়া কি মরব?</t>
+          <t>নারকেল গাছে বড় কালো রঙের শক্ত পোকা ধরেছে, গাছের মাথায় প্রায় ২ সেন্টিমিটারের মতো গর্ত করে ফেলেছে। গাছ বাঁচানোর উপায় কী?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -9334,11 +10669,11 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_848</t>
+          <t>farmer_q_12</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -9348,7 +10683,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>গত তিন বছর ধরে জাম্বুরা গাছে ফল আসছে, কিন্তু এ বছর ফলগুলো একদমই বাড়ছে না। ঝড়ের মতো সব পচে নিচে পড়ে যাচ্ছে, এর কোনো সমাধান আছে কি?</t>
+          <t>৩৩ শতাংশ জমিতে ঢেঁড়সের বীজ কতটুকু লাগবে?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -9360,21 +10695,21 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_535</t>
+          <t>farmer_q_3</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>শসা গাছে প্রচুর জালি আসছে কিন্তু বড় হওয়ার আগেই ঝরে যাচ্ছে কেন?</t>
+          <t>আম গাছে আমের গোড়ায় এমন সাদা কালো দাগ এ অবস্থায় কি করা যায়?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -9386,21 +10721,21 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_784</t>
+          <t>farmer_q_702</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>ফলের গাছের কলম করার জন্য ভালো কোনো রুটিং হরমোনের নাম বলবেন কি? কোনটা ব্যবহার করলে কলম ভালো টিকবে?</t>
+          <t>Sir can i commercially planted mata or bedana on our land. ( Patnitola, Naogaon) un fartil land. what type is good. pls sujjest.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -9412,21 +10747,21 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_828</t>
+          <t>farmer_q_403</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>অনেকদিন হলো সাত-আট বছর বয়সী আম গাছটা একদম ঝিমিয়ে আছে, ফুলও ধরছে না। গাছ সতেজ করতে আর ফুল আনতে এখন কী ধরনের সার দেওয়া উচিত?</t>
+          <t>ধানের ক্ষেতে ইঁদুরের উপদ্রব খুব, কি করুম?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -9438,21 +10773,21 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_945</t>
+          <t>farmer_q_857</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>ড্রাম অর্ধেক করে পেয়ারা গাছ লাগাতে চাচ্ছি, এভাবে কি গাছ টিকবে? পরামর্শ দিলে উপকৃত হতাম।</t>
+          <t>টানা বৃষ্টির চোটে ছাদের গাছগুলো একদম নেতিয়ে গেছে, ডালপালাও খুব দুর্বল দেখাচ্ছে। এখন গাছের যত্ন নিতে কী কী করা দরকার?</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -9464,11 +10799,11 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_608</t>
+          <t>farmer_q_441</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -9478,7 +10813,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>কম খরচে কোন সার দিলে ধান ভালো হইবো?</t>
+          <t>আলু গাছে কালো দাগ পড়তেছে, এটা কি পচন রোগ?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -9489,7 +10824,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -9518,7 +10856,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -9553,7 +10891,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -9579,21 +10917,21 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_35</t>
+          <t>farmer_q_483</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>বর্তমান আবহাওয়ায়(June, Rainy) আনারসের খেতে সার দেওয়া যাবে??</t>
+          <t>বেগুনের ডগা পচা রোগ হইছে, কি করমু বুঝতেছি না</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -9605,21 +10943,27 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_36</t>
+          <t>farmer_q_640</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>গত সোমবার ওয়ান স্টপ+ফরোয়ার্ড ঔষধ দেওয়ার পর ড্রামে কিছু ঔষধ থেকে যায় আজকে সেই ঔষধ দেওয়া যাবে?</t>
+          <t>আমি আমার বাড়ীর পাশে কিছু সংখ্যক কাঠালের চারা রুপন করি গত ৩-৪ বছর আগে।
+বিগত কয়েক বছর ধরে প্রায় সব গাছেই কাঠাল আসছে। কিন্তু আমার একটি গাছের কাঠাল পচে ঝরে যায়।
+পচার ধরন -বাইরে থেকে বুঝা যায় না , যখন কাঠাল পরিপক্ক হয় বা খাওয়ার উপযোগি হই তখন গাছ থেকে পেড়ে নিই।
+বড়ই দুঃখের বিষয় এই যে পাকার জন্য রেখে দিলে পরে দেখা যাই মুলি(মুল দন্ড যার চার পাশে কোষ থাকে) পচে যায় ও কাঠালে দুর্ঘ্নদ সৃস্টি হয় ফলে খাওার উপযোগি থাকেনা।
+ভেবে ছিলাম আমাদের পাকানোর কোন ভুল তাই পরবর্তি বছর মানে এই মৌসোম এ কাঠাল গাছে পাকানোর সিদ্ধান্ত নিই ।কিন্তু
+যখন দেখতে পেলাম কাঠাল গাছেই পূর্বে বর্ণিত অবস্থায় পচে যাচ্ছে তখন খুভই মর্মাহত হলাম।
+আমি এর সঠিক সমাধান চাই। ধন্যবাদ</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -9631,21 +10975,23 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_792</t>
+          <t>farmer_q_667</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>১২ বছরের পুরনো কাজু গাছে ফুল তো প্রচুর দেখি, কিন্তু ফল আর দেখা যায় না। ৪-৫ বছর ধরে একই অবস্থা, মার্চ মাসে ফুল আসে আর শুকিয়ে পড়ে যায়। সমাধানটা একটু জানাবেন?</t>
+          <t>আম গাছের বৃদ্ধি হয়না ও ফুল ধরে না। গাছের বয়স ৭-৮ বছর।
+এখন কি ধরনের সার দিতে হবে?
+ধন্যবাদ।।</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -9657,21 +11003,21 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_914</t>
+          <t>farmer_q_528</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>ছাদে বাগান করার শখ আছে, কিন্তু বাজেটটা কত রাখা উচিত বুঝতে পারছি না। খরচাপাতি কেমন পড়বে?</t>
+          <t>কলা গাছের গোড়ায় কি যেন লালচে দাগ, এটা কি রোগ?</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -9683,21 +11029,21 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_549</t>
+          <t>farmer_q_321</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>বোরো ধানে এখন কি পটাশ দেয়া যাবে?</t>
+          <t>গম চাষে আগাছা দমনে কি করব?</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -9709,21 +11055,21 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_47</t>
+          <t>farmer_q_634</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>রুপনের বয়স ১৪দিন।গোরা পোচার জন্য কোন ছত্রাক নাশক ও কীটনাশক  দিবো?</t>
+          <t>angor geser pata bindo bindo hoea pataer majkan shokea jea.porea pata jora jea.pls help me. sir.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -9735,11 +11081,11 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_606</t>
+          <t>farmer_q_507</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -9749,7 +11095,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>বোরো ধানে মাজরা পোকা কি বেশি হইছে?</t>
+          <t>কলা গাছে কি যেন কালো দাগ হইছে, গাছটা কি কাইটা ফেলমু?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -9761,21 +11107,21 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_565</t>
+          <t>farmer_q_668</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>ধান পাতায় লাল দাগ কেন পরতাছে, কোনো ওষুধ আছে?</t>
+          <t>about good papaw seet  where</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -9787,21 +11133,21 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_665</t>
+          <t>farmer_q_40</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>মাটির উবরতা কম</t>
+          <t>জমি দুবলা ঘাসে চেপে গেছে। এই ঘাস হাল চাষের পূর্বেই নির্মূল করতে (পুড়িয়ে ফেলতে) কোন ওষুধ স্প্রে করলে ভালো ফলাফল পাওয়া যাবে?</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -9813,21 +11159,21 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_459</t>
+          <t>farmer_q_648</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>ধান পাকার আগে জল কি বন্ধ করে দিতে হয়?</t>
+          <t>নারকেল গাছে একধরনের বড় বিটল জাতীয় পোকা গাছ খেয়ে ফেলছে।পোকা দেখতে কালো ও শক্ত আবরন।পোকার গর্তের পরিধি আনুমানিক 2cm প্রায়। করনীয় কি।</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -9839,11 +11185,11 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_836</t>
+          <t>farmer_q_111</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -9853,7 +11199,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>আমার পেয়ারা বাগানে সাদা সাদা পোকা ধরেছে, এগুলো দমনের জন্য ভালো কোনো কীটনাশকের নাম বলতে পারবেন?</t>
+          <t>আলুর নাভি ধসা রোগ থেকে বাঁচতে কী করণীয়?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -9865,11 +11211,11 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_997</t>
+          <t>farmer_q_840</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -9879,7 +11225,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>বৈশাখ মাসে বাঁশঝাড়ের গোড়ায় মাটি তো দিলাম, এখন ফলন বাড়াতে কী সার দিলে ভালো হয় একটু বলবেন?</t>
+          <t>মুরগির বাচ্চার স্বাস্থ্য ভালো রাখতে প্রাকৃতিক প্রোবায়োটিক হিসেবে কী খাওয়ানো ভালো? এমন কিছু খুঁজছি যাতে বাচ্চার পেটে উপকারী ব্যাকটেরিয়া বাড়ে।</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -9891,21 +11237,21 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_391</t>
+          <t>farmer_q_193</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>মাঠে তো সার দিলাম, তাও গাছ হলুদ হইয়া যাইতেছে কেন?</t>
+          <t>বেগুন গাছের গোড়া পচে যাচ্ছে এবং গাছ ঝিমিয়ে পড়ছে। কোন ছত্রাকনাশক ব্যবহার করলে ভালো ফল পাব?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -9917,11 +11263,11 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_632</t>
+          <t>farmer_q_420</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -9931,7 +11277,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>জমি চাষ করার পর কি কি সার আগে দিমু?</t>
+          <t>জমিতে আগাছা বেশি হইয়া গেছে, ওষুধ দিয়া কি মরব?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -9943,11 +11289,11 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_327</t>
+          <t>farmer_q_848</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -9957,7 +11303,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>পেঁয়াজ চাষে গোড়া পচা রোধে জিপসাম সারের ভূমিকা কতটুকু?</t>
+          <t>গত তিন বছর ধরে জাম্বুরা গাছে ফল আসছে, কিন্তু এ বছর ফলগুলো একদমই বাড়ছে না। ঝড়ের মতো সব পচে নিচে পড়ে যাচ্ছে, এর কোনো সমাধান আছে কি?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -9969,11 +11315,11 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_467</t>
+          <t>farmer_q_535</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -9983,7 +11329,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>পেঁপে গাছে হলুদ দাগ পড়তাছে, গাছ কি বাঁচবো?</t>
+          <t>শসা গাছে প্রচুর জালি আসছে কিন্তু বড় হওয়ার আগেই ঝরে যাচ্ছে কেন?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -9995,21 +11341,21 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_366</t>
+          <t>farmer_q_784</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>ধান কাটতে দেরি হইলে কি ক্ষতি হইব?</t>
+          <t>ফলের গাছের কলম করার জন্য ভালো কোনো রুটিং হরমোনের নাম বলবেন কি? কোনটা ব্যবহার করলে কলম ভালো টিকবে?</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -10021,11 +11367,11 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_71</t>
+          <t>farmer_q_828</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -10035,8 +11381,7 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>আমন মৌসুমে উঁচু জমিতে কোন ধান সবচেয়ে বেশি ফলন দেয়।।
-পরবর্তীতে সরিষা করার চিন্তা আছে</t>
+          <t>অনেকদিন হলো সাত-আট বছর বয়সী আম গাছটা একদম ঝিমিয়ে আছে, ফুলও ধরছে না। গাছ সতেজ করতে আর ফুল আনতে এখন কী ধরনের সার দেওয়া উচিত?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -10048,21 +11393,21 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_788</t>
+          <t>farmer_q_945</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>আমি শুনেছি সুপারির চারা ৪ হাত দূরে রোপণ করতে হয়, কিন্তু আমার বাগানে চারাগুলো ৩ হাত দূরত্বে লাগানো হয়ে গেছে। এতে কি ফলন কমে যাবে বা ভবিষ্যতে গাছের কোনো ক্ষতি হবে?</t>
+          <t>ড্রাম অর্ধেক করে পেয়ারা গাছ লাগাতে চাচ্ছি, এভাবে কি গাছ টিকবে? পরামর্শ দিলে উপকৃত হতাম।</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -10074,11 +11419,11 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_555</t>
+          <t>farmer_q_608</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -10088,7 +11433,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>মাঠে পোকা ধরছে, সব পাতা খাইয়া ফেলতাছে।</t>
+          <t>কম খরচে কোন সার দিলে ধান ভালো হইবো?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -10099,7 +11444,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -10128,7 +11476,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -10163,7 +11511,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -10189,11 +11537,11 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_235</t>
+          <t>farmer_q_35</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -10203,7 +11551,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>শীতকালীন সবজির জন্য জৈব সার কীভাবে তৈরি করবো?</t>
+          <t>বর্তমান আবহাওয়ায়(June, Rainy) আনারসের খেতে সার দেওয়া যাবে??</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -10215,21 +11563,21 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_616</t>
+          <t>farmer_q_36</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>আমার বেগুনের ডগা মরে যাচ্ছে, পোকা কি ভেতরে?</t>
+          <t>গত সোমবার ওয়ান স্টপ+ফরোয়ার্ড ঔষধ দেওয়ার পর ড্রামে কিছু ঔষধ থেকে যায় আজকে সেই ঔষধ দেওয়া যাবে?</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -10241,11 +11589,11 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_194</t>
+          <t>farmer_q_792</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -10255,7 +11603,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>শীতকালীন শিমের গাছে প্রচুর জাব পোকা দেখা যাচ্ছে। বিষ না দিয়ে দমন করার উপায় আছে কি?</t>
+          <t>১২ বছরের পুরনো কাজু গাছে ফুল তো প্রচুর দেখি, কিন্তু ফল আর দেখা যায় না। ৪-৫ বছর ধরে একই অবস্থা, মার্চ মাসে ফুল আসে আর শুকিয়ে পড়ে যায়। সমাধানটা একটু জানাবেন?</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -10267,11 +11615,11 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_119</t>
+          <t>farmer_q_914</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -10281,7 +11629,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>ধানের ক্ষেতে মাজরা পোকা দমনে জৈব পদ্ধতি আছে কি?</t>
+          <t>ছাদে বাগান করার শখ আছে, কিন্তু বাজেটটা কত রাখা উচিত বুঝতে পারছি না। খরচাপাতি কেমন পড়বে?</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -10293,21 +11641,21 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_989</t>
+          <t>farmer_q_549</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>ভাই, কোয়েল আর মাশরুমের ব্যবসা শুরু করার ইচ্ছা আছে। রংপুরে এই বিষয়ে প্রশিক্ষণ নেওয়ার মতো কোনো জায়গা আছে নাকি? এছাড়া মালপত্র কোথায় কিনব আর কোথায় বিক্রি করব তা জানালে খুব উপকার হতো।</t>
+          <t>বোরো ধানে এখন কি পটাশ দেয়া যাবে?</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -10319,11 +11667,11 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_331</t>
+          <t>farmer_q_47</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -10333,7 +11681,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>সরিষা ক্ষেতে জাব পোকা (Aphids) আক্রমণ করেছে, কী করব?</t>
+          <t>রুপনের বয়স ১৪দিন।গোরা পোচার জন্য কোন ছত্রাক নাশক ও কীটনাশক  দিবো?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -10345,21 +11693,21 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_992</t>
+          <t>farmer_q_606</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>কুমিল্লায় বারি-৪ আমের চারা কোথায় পাব একটু জানাবেন কি? এছাড়া কমলা আর মালটার মধ্যে তফাতটা কী আর আমাদের এলাকায় চাষ করার জন্য কোনটার জাত ভালো হবে বুঝতে পারছি না।</t>
+          <t>বোরো ধানে মাজরা পোকা কি বেশি হইছে?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -10371,21 +11719,21 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_734</t>
+          <t>farmer_q_565</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>নমস্কার, আমার বাগানের মরিচ, লেবু আর পেয়ারা গাছের পাতায় সাদা মাছি ভরে গেছে। গাছগুলোকে এই পোকার হাত থেকে বাঁচানোর কোনো কার্যকরী সমাধান জানালে খুব উপকার হতো।</t>
+          <t>ধান পাতায় লাল দাগ কেন পরতাছে, কোনো ওষুধ আছে?</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -10397,21 +11745,21 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_618</t>
+          <t>farmer_q_665</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>শাকের পাতা ছিদ্র ছিদ্র হইয়া গেছে, কী হইলো?</t>
+          <t>মাটির উবরতা কম</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -10423,21 +11771,21 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_316</t>
+          <t>farmer_q_459</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>পেঁপে গাছের পাতা কুকড়ে যাচ্ছে, এটি কি ভাইরাস?</t>
+          <t>ধান পাকার আগে জল কি বন্ধ করে দিতে হয়?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -10449,11 +11797,11 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_883</t>
+          <t>farmer_q_836</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -10463,7 +11811,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>আমার আম্রপালি গাছের গুটিগুলো বড় হওয়ার আগেই ঝরে যাচ্ছে, এখন কী করা যায়?</t>
+          <t>আমার পেয়ারা বাগানে সাদা সাদা পোকা ধরেছে, এগুলো দমনের জন্য ভালো কোনো কীটনাশকের নাম বলতে পারবেন?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -10475,21 +11823,21 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_114</t>
+          <t>farmer_q_997</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>বেগুন গাছে জাব পোকা ও ডগা ছিদ্রকারী পোকার আক্রমণ হয়েছে, উপায় বলুন।</t>
+          <t>বৈশাখ মাসে বাঁশঝাড়ের গোড়ায় মাটি তো দিলাম, এখন ফলন বাড়াতে কী সার দিলে ভালো হয় একটু বলবেন?</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -10501,21 +11849,21 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_937</t>
+          <t>farmer_q_391</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>আম গাছের চারা লাগানোর সঠিক নিয়মটা একটু বলবেন কি?</t>
+          <t>মাঠে তো সার দিলাম, তাও গাছ হলুদ হইয়া যাইতেছে কেন?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -10527,21 +11875,21 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_185</t>
+          <t>farmer_q_632</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>টমেটো চাষে ভালো ফলন পেতে কোন সার কতটুকু দেব?</t>
+          <t>জমি চাষ করার পর কি কি সার আগে দিমু?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -10553,21 +11901,21 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_499</t>
+          <t>farmer_q_327</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>কোন সারটা দিলে মরিচ গাছ বড় হইবো?</t>
+          <t>পেঁয়াজ চাষে গোড়া পচা রোধে জিপসাম সারের ভূমিকা কতটুকু?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -10579,21 +11927,21 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_761</t>
+          <t>farmer_q_467</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>বিষাক্ত ওষুধ না দিয়ে আম পাকানোর সহজ ও ঘরোয়া পদ্ধতি কী?</t>
+          <t>পেঁপে গাছে হলুদ দাগ পড়তাছে, গাছ কি বাঁচবো?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -10605,11 +11953,11 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_518</t>
+          <t>farmer_q_366</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -10619,7 +11967,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>টমেটো গাছে পোকা ধরছে, কোনো বিষের নাম বলবেন?</t>
+          <t>ধান কাটতে দেরি হইলে কি ক্ষতি হইব?</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -10631,21 +11979,22 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_845</t>
+          <t>farmer_q_71</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>গাছটার বয়স অনেক হলো, কিন্তু এখন দেখছি পাতার ধারগুলো চিরে গেছে আর মাথাটা মরে যাচ্ছে। নারিকেল বড় হচ্ছে না, উল্টো ঝরে পড়ে যাচ্ছে; এর কোনো ওষুধ বা প্রতিকার আছে কি?</t>
+          <t>আমন মৌসুমে উঁচু জমিতে কোন ধান সবচেয়ে বেশি ফলন দেয়।।
+পরবর্তীতে সরিষা করার চিন্তা আছে</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -10657,21 +12006,21 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_52</t>
+          <t>farmer_q_788</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>ডালিম গাছ হঠাৎ করে পাতাগুলো লাল হয়ে গাছ মরে যাচ্ছে। এখন করনীয় কি সবার পরামর্শ চাচ্ছি?</t>
+          <t>আমি শুনেছি সুপারির চারা ৪ হাত দূরে রোপণ করতে হয়, কিন্তু আমার বাগানে চারাগুলো ৩ হাত দূরত্বে লাগানো হয়ে গেছে। এতে কি ফলন কমে যাবে বা ভবিষ্যতে গাছের কোনো ক্ষতি হবে?</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -10683,11 +12032,11 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_623</t>
+          <t>farmer_q_555</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -10697,7 +12046,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>সরষে গাছে পোকা ধরছে, কোন বিষ দিব?</t>
+          <t>মাঠে পোকা ধরছে, সব পাতা খাইয়া ফেলতাছে।</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -10708,7 +12057,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -10737,7 +12089,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -10772,7 +12124,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -10798,21 +12150,21 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_450</t>
+          <t>farmer_q_235</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>মাটি কি পরীক্ষা করানো লাগে? ফলন তো আগের মতো পাই না।</t>
+          <t>শীতকালীন সবজির জন্য জৈব সার কীভাবে তৈরি করবো?</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -10824,21 +12176,21 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_214</t>
+          <t>farmer_q_616</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>টমেটোর পাতা কোঁকড়ানো রোগ দূর করার উপায় কী?</t>
+          <t>আমার বেগুনের ডগা মরে যাচ্ছে, পোকা কি ভেতরে?</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -10850,11 +12202,11 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_22</t>
+          <t>farmer_q_194</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -10864,8 +12216,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>পাটের জমিতে হিউমিক এসিড স্প্রে ভালো নাকি
-সারের সাথে মাটিতে দেওয়া ভালো?</t>
+          <t>শীতকালীন শিমের গাছে প্রচুর জাব পোকা দেখা যাচ্ছে। বিষ না দিয়ে দমন করার উপায় আছে কি?</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -10877,11 +12228,11 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_142</t>
+          <t>farmer_q_119</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -10891,7 +12242,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>আমের মুকুল ঝরা রোধে কী ব্যবস্থা নেওয়া প্রয়োজন?</t>
+          <t>ধানের ক্ষেতে মাজরা পোকা দমনে জৈব পদ্ধতি আছে কি?</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -10903,21 +12254,21 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_308</t>
+          <t>farmer_q_989</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>পেয়ারা গাছের কান্ডে আঠালো রস বের হচ্ছে, গাছ দুর্বল হয়ে পড়ছে। প্রতিকার কী?</t>
+          <t>ভাই, কোয়েল আর মাশরুমের ব্যবসা শুরু করার ইচ্ছা আছে। রংপুরে এই বিষয়ে প্রশিক্ষণ নেওয়ার মতো কোনো জায়গা আছে নাকি? এছাড়া মালপত্র কোথায় কিনব আর কোথায় বিক্রি করব তা জানালে খুব উপকার হতো।</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -10929,21 +12280,21 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_469</t>
+          <t>farmer_q_331</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>জমিতে পানি জমে আছে, এখন কি আর ধান লাগানো যাবে?</t>
+          <t>সরিষা ক্ষেতে জাব পোকা (Aphids) আক্রমণ করেছে, কী করব?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -10955,21 +12306,21 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_844</t>
+          <t>farmer_q_992</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>আমাদের ৪০ বছরের পুরনো নারিকেল গাছটার পাতাগুলো কেমন যেন খণ্ড খণ্ড হয়ে খাওয়া, আর আগাটা শুকিয়ে যাচ্ছে। গাছে নতুন নারিকেল আসছে না, যা-ও আছে সেগুলো ঝরে যাচ্ছে; এখন কী করব?</t>
+          <t>কুমিল্লায় বারি-৪ আমের চারা কোথায় পাব একটু জানাবেন কি? এছাড়া কমলা আর মালটার মধ্যে তফাতটা কী আর আমাদের এলাকায় চাষ করার জন্য কোনটার জাত ভালো হবে বুঝতে পারছি না।</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -10981,21 +12332,21 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_538</t>
+          <t>farmer_q_734</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>শসা গাছে প্রচুর জালি আসছে না কেন?</t>
+          <t>নমস্কার, আমার বাগানের মরিচ, লেবু আর পেয়ারা গাছের পাতায় সাদা মাছি ভরে গেছে। গাছগুলোকে এই পোকার হাত থেকে বাঁচানোর কোনো কার্যকরী সমাধান জানালে খুব উপকার হতো।</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -11007,11 +12358,11 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_530</t>
+          <t>farmer_q_618</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -11021,7 +12372,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>ডাটা শাকের পাতায় ফুটো ফুটো, কি স্প্রে করুম?</t>
+          <t>শাকের পাতা ছিদ্র ছিদ্র হইয়া গেছে, কী হইলো?</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -11033,11 +12384,11 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_172</t>
+          <t>farmer_q_316</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -11047,7 +12398,7 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>ধানের জমিতে ইউরিয়া সারের অপচয় কমাতে কী করা যায়?</t>
+          <t>পেঁপে গাছের পাতা কুকড়ে যাচ্ছে, এটি কি ভাইরাস?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -11059,21 +12410,21 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_763</t>
+          <t>farmer_q_883</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>গাছে প্রচুর কাঁঠালের মুচি এসেছিল, কিন্তু সব ছোট থাকতেই কালো হয়ে পচে ঝরে যাচ্ছে। একটা কাঁঠালও টিকছে না, কী করব?</t>
+          <t>আমার আম্রপালি গাছের গুটিগুলো বড় হওয়ার আগেই ঝরে যাচ্ছে, এখন কী করা যায়?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -11085,11 +12436,11 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_712</t>
+          <t>farmer_q_114</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -11099,7 +12450,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Amon dhan bijtolar poka domon.</t>
+          <t>বেগুন গাছে জাব পোকা ও ডগা ছিদ্রকারী পোকার আক্রমণ হয়েছে, উপায় বলুন।</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -11111,21 +12462,21 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_889</t>
+          <t>farmer_q_937</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>ভাই, আমি নতুন করে গরুর খামার শুরু করতে চাই, আসলে কোন দিক দিয়ে শুরু করলে ভালো হয় একটু বলবেন?</t>
+          <t>আম গাছের চারা লাগানোর সঠিক নিয়মটা একটু বলবেন কি?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -11137,21 +12488,21 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_416</t>
+          <t>farmer_q_185</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>ধানের শিষ সাদা হইয়া যাইতেছে, এটার নাম কি রোগ?</t>
+          <t>টমেটো চাষে ভালো ফলন পেতে কোন সার কতটুকু দেব?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -11163,21 +12514,21 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_745</t>
+          <t>farmer_q_499</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>আমার কাঠাল গাছের কাঠালগুলো বাইরে থেকে ভালো দেখালেও পাকলে ভেতর থেকে পচে যায় এবং দুর্গন্ধ বের হয়, এমনকি গাছে থাকা অবস্থায়ও এমন হচ্ছে। এর কোনো প্রতিকার আছে কি?</t>
+          <t>কোন সারটা দিলে মরিচ গাছ বড় হইবো?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -11189,21 +12540,21 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_287</t>
+          <t>farmer_q_761</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>আলুর জমিতে লেট ব্লাইট বা মড়ক রোগ থেকে বাঁচার উপায় কী?</t>
+          <t>বিষাক্ত ওষুধ না দিয়ে আম পাকানোর সহজ ও ঘরোয়া পদ্ধতি কী?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -11215,21 +12566,21 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_279</t>
+          <t>farmer_q_518</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>লেবু গাছে ক্যাংকার বা পাতায় বাদামী দাগ পড়ছে, এর সমাধান কী?</t>
+          <t>টমেটো গাছে পোকা ধরছে, কোনো বিষের নাম বলবেন?</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -11241,21 +12592,21 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_588</t>
+          <t>farmer_q_845</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>ভুট্টা ক্ষেতে ইঁদুরের উপদ্রব খুব বাড়ছে, কি করুম ভাই?</t>
+          <t>গাছটার বয়স অনেক হলো, কিন্তু এখন দেখছি পাতার ধারগুলো চিরে গেছে আর মাথাটা মরে যাচ্ছে। নারিকেল বড় হচ্ছে না, উল্টো ঝরে পড়ে যাচ্ছে; এর কোনো ওষুধ বা প্রতিকার আছে কি?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -11267,21 +12618,21 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_527</t>
+          <t>farmer_q_52</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>আমার মরিচ গাছের ডগা সব পইড়া যাইতেছে, কোনো ওষুধ আছে?</t>
+          <t>ডালিম গাছ হঠাৎ করে পাতাগুলো লাল হয়ে গাছ মরে যাচ্ছে। এখন করনীয় কি সবার পরামর্শ চাচ্ছি?</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -11293,21 +12644,21 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_874</t>
+          <t>farmer_q_623</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>আমি মুরগি, মাছ আর সবজি চাষের সমন্বিত খামার করতে চাই, কিন্তু এ বিষয়ে হাতে-কলমে শেখার জন্য ভালো কোনো প্রশিক্ষণের খোঁজ পাচ্ছি না। কোথায় গেলে এই বিষয়ে স্বল্পমেয়াদী প্রশিক্ষণ নিতে পারব জানাবেন কি?</t>
+          <t>সরষে গাছে পোকা ধরছে, কোন বিষ দিব?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -11318,7 +12669,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -11347,7 +12701,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -11382,7 +12736,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Crop Taxonomy (English)</t>
+          <t>Crop Taxonomy (English) [Dropdown]</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -11408,21 +12762,21 @@
     </row>
     <row r="2" ht="54" customHeight="1">
       <c r="A2" s="5" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_181</t>
+          <t>farmer_q_450</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>সরিষার ফুল আসার পর জাব পোকার আক্রমণ হয়েছে, এখন কি বিষ দেওয়া যাবে?</t>
+          <t>মাটি কি পরীক্ষা করানো লাগে? ফলন তো আগের মতো পাই না।</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -11434,21 +12788,21 @@
     </row>
     <row r="3" ht="54" customHeight="1">
       <c r="A3" s="10" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_361</t>
+          <t>farmer_q_214</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>মাটি শক্ত হইয়া গেছে, এখন কি করুম?</t>
+          <t>টমেটোর পাতা কোঁকড়ানো রোগ দূর করার উপায় কী?</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr"/>
@@ -11460,21 +12814,22 @@
     </row>
     <row r="4" ht="54" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_365</t>
+          <t>farmer_q_22</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>ফুলকপি চাষে পোকা ধরলে কি বিষ দেওয়া ভালো না অন্য কিছু?</t>
+          <t>পাটের জমিতে হিউমিক এসিড স্প্রে ভালো নাকি
+সারের সাথে মাটিতে দেওয়া ভালো?</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -11486,11 +12841,11 @@
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="10" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_13</t>
+          <t>farmer_q_142</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -11500,7 +12855,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>করলা গাছের ছোট ছোট ফল হয়ে ঝরে পরতিছে 🥲 এর প্রতিকার কিভাবে করবো??</t>
+          <t>আমের মুকুল ঝরা রোধে কী ব্যবস্থা নেওয়া প্রয়োজন?</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr"/>
@@ -11512,11 +12867,11 @@
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_772</t>
+          <t>farmer_q_308</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -11526,7 +12881,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>বাড়িতে একটা খুব ভালো জাতের আমড়া গাছ আছে যা বছরে দুইবার ফল দেয়, কিন্তু ঘর বড় করার জন্য গাছটা কাটতে হবে। আমি এই জাতটা বাঁচাতে চাই, আমড়া গাছে কলম করার নিয়মটা একটু বলবেন?</t>
+          <t>পেয়ারা গাছের কান্ডে আঠালো রস বের হচ্ছে, গাছ দুর্বল হয়ে পড়ছে। প্রতিকার কী?</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -11538,11 +12893,11 @@
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="10" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_569</t>
+          <t>farmer_q_469</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -11552,7 +12907,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>ধানের পাতায় কেমন জানি লালচে দাগ পড়ছে, কী করমু?</t>
+          <t>জমিতে পানি জমে আছে, এখন কি আর ধান লাগানো যাবে?</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr"/>
@@ -11564,21 +12919,21 @@
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_461</t>
+          <t>farmer_q_844</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>বেগুন গাছে পোকা লেগেছে, কোনো ভালো কীটনাশকের নাম বলবেন?</t>
+          <t>আমাদের ৪০ বছরের পুরনো নারিকেল গাছটার পাতাগুলো কেমন যেন খণ্ড খণ্ড হয়ে খাওয়া, আর আগাটা শুকিয়ে যাচ্ছে। গাছে নতুন নারিকেল আসছে না, যা-ও আছে সেগুলো ঝরে যাচ্ছে; এখন কী করব?</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -11590,21 +12945,21 @@
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="10" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_274</t>
+          <t>farmer_q_538</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>ধানের পাতায় মরিচা বা ব্লাস্ট রোগ দেখা দিয়েছে। কি করলে ফলন রক্ষা করা যাবে?</t>
+          <t>শসা গাছে প্রচুর জালি আসছে না কেন?</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr"/>
@@ -11616,22 +12971,21 @@
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_687</t>
+          <t>farmer_q_530</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>ভাই, আসসালামুআলাইকুম।
-আমি একজন মাশরুম চাষী। আমার বর্তমানে ৫০০০ খরের প্যাকেট (১২*১৮) আআছে।ওয়েস্টার ws +po2 জাতের কিন্তু ফলন তুলনা মূলক অনেক কম হচ্ছে।দয়াকরে ফলন কি ভাবে বাড়ানো যায় জানাবেন কি ? মোবাইল নং ০১৭৫২-৪১২২৫৫। আপনাদের সাথে যোগাযোগের মোবাইল নং দেবেন plz.</t>
+          <t>ডাটা শাকের পাতায় ফুটো ফুটো, কি স্প্রে করুম?</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -11643,21 +12997,21 @@
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="10" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_603</t>
+          <t>farmer_q_172</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>fb_group_real_farmer</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>শসা গাছে হলুদ হলুদ কি যেন হইতাছে, কোনো ওষুধ আছে?</t>
+          <t>ধানের জমিতে ইউরিয়া সারের অপচয় কমাতে কী করা যায়?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr"/>
@@ -11669,21 +13023,21 @@
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_572</t>
+          <t>farmer_q_763</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>কীটনাশক দেওয়ার পর বৃষ্টি আইলে কি আবার দিতে হইবো?</t>
+          <t>গাছে প্রচুর কাঁঠালের মুচি এসেছিল, কিন্তু সব ছোট থাকতেই কালো হয়ে পচে ঝরে যাচ্ছে। একটা কাঁঠালও টিকছে না, কী করব?</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -11695,11 +13049,11 @@
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="10" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_229</t>
+          <t>farmer_q_712</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -11709,7 +13063,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>আমার শসা গাছে পাতার ওপর হলুদ মোজাইক আকৃতির দাগ দেখা যাচ্ছে, এটি কি ভাইরাস?</t>
+          <t>Amon dhan bijtolar poka domon.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr"/>
@@ -11721,11 +13075,11 @@
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_654</t>
+          <t>farmer_q_889</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -11735,7 +13089,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>আমি জেনেছি,সুপারী গাছ ৪হাত দুরত্বে রোপণ করতে হয়।কিন্তু আমি ৩হাত দুরত্বে রোপন করে ফেলেছি।এখন কি সুপারি ধরবে?</t>
+          <t>ভাই, আমি নতুন করে গরুর খামার শুরু করতে চাই, আসলে কোন দিক দিয়ে শুরু করলে ভালো হয় একটু বলবেন?</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -11747,21 +13101,21 @@
     </row>
     <row r="15" ht="54" customHeight="1">
       <c r="A15" s="10" t="n">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_950</t>
+          <t>farmer_q_416</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>ভাই, লাউ গাছ তো অনেক বড় হলো, কিন্তু একটাও ফুল ফুটছে না। কী করব?</t>
+          <t>ধানের শিষ সাদা হইয়া যাইতেছে, এটার নাম কি রোগ?</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr"/>
@@ -11773,21 +13127,21 @@
     </row>
     <row r="16" ht="54" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_404</t>
+          <t>farmer_q_745</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>field_sourced_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>সবজি বাগানে কি খৈল পচা সার দেওয়া ঠিক হবে?</t>
+          <t>আমার কাঠাল গাছের কাঠালগুলো বাইরে থেকে ভালো দেখালেও পাকলে ভেতর থেকে পচে যায় এবং দুর্গন্ধ বের হয়, এমনকি গাছে থাকা অবস্থায়ও এমন হচ্ছে। এর কোনো প্রতিকার আছে কি?</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -11799,11 +13153,11 @@
     </row>
     <row r="17" ht="54" customHeight="1">
       <c r="A17" s="10" t="n">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_295</t>
+          <t>farmer_q_287</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -11813,7 +13167,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>শীতকালীন সবজির জন্য এনপিকে (NPK) সারের সঠিক অনুপাত কী হওয়া উচিত?</t>
+          <t>আলুর জমিতে লেট ব্লাইট বা মড়ক রোগ থেকে বাঁচার উপায় কী?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
@@ -11825,11 +13179,11 @@
     </row>
     <row r="18" ht="54" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_739</t>
+          <t>farmer_q_279</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -11839,7 +13193,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>আমার লেবু গাছের পাতাগুলো হলুদ হয়ে শুকিয়ে যাচ্ছে, আর পাতার নিচে সাদা সাদা দাগ দেখা যাচ্ছে। এর জন্য কী করতে পারি?</t>
+          <t>লেবু গাছে ক্যাংকার বা পাতায় বাদামী দাগ পড়ছে, এর সমাধান কী?</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -11851,11 +13205,11 @@
     </row>
     <row r="19" ht="54" customHeight="1">
       <c r="A19" s="10" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_631</t>
+          <t>farmer_q_588</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -11865,7 +13219,7 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>একটু কম খরচে কী সার দেওয়া যায়?</t>
+          <t>ভুট্টা ক্ষেতে ইঁদুরের উপদ্রব খুব বাড়ছে, কি করুম ভাই?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
@@ -11877,21 +13231,21 @@
     </row>
     <row r="20" ht="54" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>farmer_q_961</t>
+          <t>farmer_q_527</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>krishibangla.com</t>
+          <t>field_sourced_farmer</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>আমন ধানের বীজতলায় পোকা ধরেছে, এখন কী করলে ভালো হয়?</t>
+          <t>আমার মরিচ গাছের ডগা সব পইড়া যাইতেছে, কোনো ওষুধ আছে?</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -11903,21 +13257,21 @@
     </row>
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="10" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>farmer_q_904</t>
+          <t>farmer_q_874</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>fb_group_real_farmer</t>
+          <t>krishibangla.com</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>ভাই, ছাদ বাগান করার ওপর কোনো ট্রেনিংয়ের ব্যবস্থা আছে কি? থাকলে কোথায় যোগাযোগ করব জানাবেন?</t>
+          <t>আমি মুরগি, মাছ আর সবজি চাষের সমন্বিত খামার করতে চাই, কিন্তু এ বিষয়ে হাতে-কলমে শেখার জন্য ভালো কোনো প্রশিক্ষণের খোঁজ পাচ্ছি না। কোথায় গেলে এই বিষয়ে স্বল্পমেয়াদী প্রশিক্ষণ নিতে পারব জানাবেন কি?</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -11928,7 +13282,10 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Reference_and_Examples!$A$5:$A$41</formula1>
+    </dataValidation>
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
